--- a/feedback_surveys/044_training_satisfaction_indicator_survey--feedback_surveys.xlsx
+++ b/feedback_surveys/044_training_satisfaction_indicator_survey--feedback_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -702,12 +702,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'highly_satisfied'}</t>
+          <t>highly_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Highly Satisfied'}</t>
+          <t>Highly Satisfied</t>
         </is>
       </c>
     </row>
@@ -719,12 +719,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'neither_satisfied_nor_dissatisfied'}</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Neither Satisfied nor Dissatisfied'}</t>
+          <t>Neither Satisfied nor Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -753,12 +753,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -787,12 +787,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'the_training_session_met_my_expectations'}</t>
+          <t>the_training_session_met_my_expectations</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'The training session met my expectations'}</t>
+          <t>The training session met my expectations</t>
         </is>
       </c>
     </row>
@@ -804,12 +804,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'the_training_session_exceeded_my_expectations'}</t>
+          <t>the_training_session_exceeded_my_expectations</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'The training session exceeded my expectations'}</t>
+          <t>The training session exceeded my expectations</t>
         </is>
       </c>
     </row>
@@ -821,12 +821,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'the_training_session_fell_short_of_my_expectations'}</t>
+          <t>the_training_session_fell_short_of_my_expectations</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'The training session fell short of my expectations'}</t>
+          <t>The training session fell short of my expectations</t>
         </is>
       </c>
     </row>
@@ -838,12 +838,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'the_training_session_was_average'}</t>
+          <t>the_training_session_was_average</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'The training session was average'}</t>
+          <t>The training session was average</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'i_did_not_attend_the_training_session'}</t>
+          <t>i_did_not_attend_the_training_session</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'I did not attend the training session'}</t>
+          <t>I did not attend the training session</t>
         </is>
       </c>
     </row>
